--- a/Predictions/2026-06-20.xlsx
+++ b/Predictions/2026-06-20.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B827A7F-8938-4B7C-BD65-40D675DABFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D08A6F0-230D-4A74-A1D7-33892A13A33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
   <si>
     <t>Red Corner</t>
   </si>
@@ -134,18 +134,6 @@
   </si>
   <si>
     <t>Model</t>
-  </si>
-  <si>
-    <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>Grok</t>
-  </si>
-  <si>
-    <t>Gemini</t>
-  </si>
-  <si>
-    <t>Claude</t>
   </si>
   <si>
     <t>Glicko-2</t>
@@ -174,6 +162,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -240,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -248,16 +237,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -562,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -577,48 +569,24 @@
     <col min="10" max="10" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D1" s="4" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="T1" s="4"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,37 +618,13 @@
         <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -690,59 +634,35 @@
       <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>0.58522569393508561</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <v>0.41036739315083809</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>0.35051753902123511</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <v>0.41036739315083809</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="4">
         <v>0.2391150678279268</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="7">
         <v>0.54900000000000004</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -752,59 +672,35 @@
       <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>0.64793925696603138</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>0.40631227406963832</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>0.3535767807052409</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>0.40631227406963832</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>0.2401109452251208</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <v>0.63500000000000001</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -814,59 +710,35 @@
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>0.81192499467594192</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <v>0.41652643990246341</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>0.41652643990246341</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>0.33526923228987943</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="7">
         <v>0.24820432780765719</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <v>0.69599999999999995</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -876,59 +748,35 @@
       <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>0.63151663240208955</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="7">
         <v>0.36592464754212739</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="7">
         <v>0.36592464754212739</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="7">
         <v>0.28264388908177668</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="7">
         <v>0.35143146337609588</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="7">
         <v>0.51500000000000001</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -938,59 +786,35 @@
       <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>0.82010474070854422</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>0.42618380797337468</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>0.42618380797337468</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <v>0.26536787979053272</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="7">
         <v>0.30844831223609248</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="7">
         <v>0.78200000000000003</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1000,59 +824,35 @@
       <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>0.60460881696505875</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>0.42513328303992293</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>0.3381905425526916</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <v>0.42513328303992293</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="7">
         <v>0.2366761744073855</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <v>0.503</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1062,59 +862,35 @@
       <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>0.71395211206975029</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>0.41570580847216237</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>0.34915056582890519</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>0.23514362569893241</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <v>0.41570580847216237</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
         <v>0.63500000000000001</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -1124,59 +900,35 @@
       <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>0.61900287976342694</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <v>0.403575613557212</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <v>0.39316070873782399</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <v>0.20326367770496401</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="7">
         <v>0.403575613557212</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="7">
         <v>0.74099999999999999</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>33</v>
       </c>
@@ -1186,59 +938,35 @@
       <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="7">
         <v>0.62435344006609961</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="7">
         <v>0.39187070800450607</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="7">
         <v>0.3428876285642255</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="7">
         <v>0.39187070800450607</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="7">
         <v>0.26524166343126843</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="7">
         <v>0.50900000000000001</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -1248,65 +976,37 @@
       <c r="C12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>0.64264906121061405</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>0.46945212434878369</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>0.46945212434878369</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <v>0.21856122171454251</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="4">
         <v>0.31198665393667391</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="4">
         <v>0.61199999999999999</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>20</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="2">
     <mergeCell ref="D1:J1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
